--- a/data/trans_dic/P79$recibos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P79$recibos_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,67</t>
+          <t>1,76; 4,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,31</t>
+          <t>2,45; 5,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,35</t>
+          <t>2,48; 4,55</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,44</t>
+          <t>4,02; 8,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,23</t>
+          <t>4,84; 9,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,91</t>
+          <t>4,75; 7,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,53</t>
+          <t>7,47; 12,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,9</t>
+          <t>4,64; 11,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,82</t>
+          <t>7,24; 11,62</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,23</t>
+          <t>8,35; 12,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,57</t>
+          <t>5,75; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,79</t>
+          <t>7,64; 10,29</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 17,08</t>
+          <t>10,63; 16,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,96; 15,92</t>
+          <t>12,8; 17,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,42; 15,23</t>
+          <t>12,46; 16,4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 13,16</t>
+          <t>2,79; 12,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,1; 16,12</t>
+          <t>11,14; 15,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 14,21</t>
+          <t>9,77; 14,07</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,56</t>
+          <t>7,67; 9,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 9,87</t>
+          <t>8,89; 10,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,07</t>
+          <t>8,58; 9,97</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>34474</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8553; 23370</t>
+          <t>9584; 25144</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9506; 23366</t>
+          <t>11751; 26964</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21212; 40886</t>
+          <t>25421; 46621</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>56600</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17673; 37628</t>
+          <t>19138; 40430</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17351; 34931</t>
+          <t>20274; 39585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40203; 65239</t>
+          <t>42516; 71201</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>60047</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14197; 69254</t>
+          <t>34380; 59522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8491; 19623</t>
+          <t>8597; 21351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24697; 80798</t>
+          <t>46727; 75035</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143490</t>
+          <t>171462</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>73936; 113985</t>
+          <t>92641; 135849</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25109; 71788</t>
+          <t>47567; 74001</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95661; 172639</t>
+          <t>148019; 199320</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>72226</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161019</t>
+          <t>190373</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47547; 77471</t>
+          <t>56682; 90326</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81412; 118235</t>
+          <t>102015; 138975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136608; 182174</t>
+          <t>165834; 218252</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>104707</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>119210</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4243; 28192</t>
+          <t>5943; 27352</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79666; 115709</t>
+          <t>88767; 123824</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87293; 132492</t>
+          <t>98617; 142086</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>288027</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>632166</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>189342; 281407</t>
+          <t>256062; 324119</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>239750; 334891</t>
+          <t>311457; 376785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>472955; 606074</t>
+          <t>586807; 682161</t>
         </is>
       </c>
     </row>
